--- a/Add_New_Project.xlsx
+++ b/Add_New_Project.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nsain\Documents\Service_cost_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F307D213-453E-41E8-8551-13B3F5E392A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16FA8784-B84C-44C5-9DF8-0931D36E8BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1BC305EA-60A5-486F-8317-C777F564B99C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7714C22E-E722-4EEE-9447-C8BD6B5226F9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Add New Project" sheetId="1" r:id="rId1"/>
+    <sheet name="Add_New_Project" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Add_New_Project!$A$1:$H$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,68 +34,89 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>BU</t>
-  </si>
-  <si>
-    <t>CT_Description</t>
-  </si>
-  <si>
-    <t>Customer_L05</t>
-  </si>
-  <si>
-    <t>Project/AMC</t>
-  </si>
-  <si>
-    <t>LOA_ID</t>
-  </si>
-  <si>
-    <t>LOA_Name</t>
-  </si>
-  <si>
-    <t>Project View</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+  <si>
+    <t>Business Division (BD)</t>
+  </si>
+  <si>
+    <t>CT name (Reported Cust)</t>
+  </si>
+  <si>
+    <t>Opportunity Code</t>
+  </si>
+  <si>
+    <t>Project Description</t>
+  </si>
+  <si>
+    <t>WBS Type</t>
+  </si>
+  <si>
+    <t>WBS</t>
+  </si>
+  <si>
+    <t>WBS Description</t>
+  </si>
+  <si>
+    <t>Merged</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>INDIA BH CT Bharti</t>
+  </si>
+  <si>
+    <t>24.IN.378121</t>
+  </si>
+  <si>
+    <t>5G Backhaul 2025</t>
+  </si>
+  <si>
+    <t>Project</t>
   </si>
   <si>
     <t>WBS1</t>
   </si>
   <si>
+    <t>WBS1 Description</t>
+  </si>
+  <si>
+    <t>WBS1, WBS2, WBS3, WBS4, WBS5</t>
+  </si>
+  <si>
     <t>WBS2</t>
   </si>
   <si>
+    <t>WBS2 Description</t>
+  </si>
+  <si>
     <t>WBS3</t>
   </si>
   <si>
+    <t>WBS3 Description</t>
+  </si>
+  <si>
     <t>WBS4</t>
   </si>
   <si>
+    <t>WBS4 Description</t>
+  </si>
+  <si>
+    <t>Warranty/Other</t>
+  </si>
+  <si>
     <t>WBS5</t>
   </si>
   <si>
-    <t>WBS6</t>
-  </si>
-  <si>
-    <t>WBS7</t>
-  </si>
-  <si>
-    <t>WBS8</t>
-  </si>
-  <si>
-    <t>WBS9</t>
-  </si>
-  <si>
-    <t>WBS10</t>
-  </si>
-  <si>
-    <t>WBS11</t>
-  </si>
-  <si>
-    <t>WBS12</t>
+    <t>WBS5 Description</t>
   </si>
 </sst>
 </file>
@@ -108,12 +132,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -128,8 +158,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,77 +494,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BBCDCE-2250-419E-87C7-F05CE54F9026}">
-  <dimension ref="A1:S1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD6F9ED-7166-45E2-ACE4-3F471C95495C}">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H6" xr:uid="{C0B66472-2CE3-44D8-9452-2C8437652007}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Add_New_Project.xlsx
+++ b/Add_New_Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nsain\Documents\Service_cost_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16FA8784-B84C-44C5-9DF8-0931D36E8BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93581F3-3B9A-42CD-9691-2869A163CAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7714C22E-E722-4EEE-9447-C8BD6B5226F9}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Business Division (BD)</t>
   </si>
@@ -66,67 +66,23 @@
   </si>
   <si>
     <t>Merged</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>INDIA BH CT Bharti</t>
-  </si>
-  <si>
-    <t>24.IN.378121</t>
-  </si>
-  <si>
-    <t>5G Backhaul 2025</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>WBS1</t>
-  </si>
-  <si>
-    <t>WBS1 Description</t>
-  </si>
-  <si>
-    <t>WBS1, WBS2, WBS3, WBS4, WBS5</t>
-  </si>
-  <si>
-    <t>WBS2</t>
-  </si>
-  <si>
-    <t>WBS2 Description</t>
-  </si>
-  <si>
-    <t>WBS3</t>
-  </si>
-  <si>
-    <t>WBS3 Description</t>
-  </si>
-  <si>
-    <t>WBS4</t>
-  </si>
-  <si>
-    <t>WBS4 Description</t>
-  </si>
-  <si>
-    <t>Warranty/Other</t>
-  </si>
-  <si>
-    <t>WBS5</t>
-  </si>
-  <si>
-    <t>WBS5 Description</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -158,9 +114,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD6F9ED-7166-45E2-ACE4-3F471C95495C}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -530,94 +487,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6" xr:uid="{C0B66472-2CE3-44D8-9452-2C8437652007}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>